--- a/R_Scripts/gse_metadata_full.xlsx
+++ b/R_Scripts/gse_metadata_full.xlsx
@@ -1,22 +1,572 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2dc6ddbe4b51f030/Documents/GitHub/GEO_Data_Pulling/R_Scripts/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="2" documentId="11_BF76FA97192180A5CC7EAF4F5AAE453645B51FCD" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B1958A51-E575-416D-A11D-573779A33D3A}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="3720" yWindow="465" windowWidth="16605" windowHeight="13665" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Metadata" sheetId="1" r:id="rId1"/>
     <sheet name="Failed" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="179">
+  <si>
+    <t>GEO Series ID (GSE___)</t>
+  </si>
+  <si>
+    <t>Data type</t>
+  </si>
+  <si>
+    <t>SuperSeries, list GEO Series that are part of the SuperSeries</t>
+  </si>
+  <si>
+    <t>Sample size (placenta)</t>
+  </si>
+  <si>
+    <t>Title</t>
+  </si>
+  <si>
+    <t>Organism</t>
+  </si>
+  <si>
+    <t>Characteristics</t>
+  </si>
+  <si>
+    <t>Extracted molecule</t>
+  </si>
+  <si>
+    <t>Extraction protocol</t>
+  </si>
+  <si>
+    <t>Library Strategy</t>
+  </si>
+  <si>
+    <t>Library source</t>
+  </si>
+  <si>
+    <t>Library selection</t>
+  </si>
+  <si>
+    <t>Instrument model</t>
+  </si>
+  <si>
+    <t>Assay description</t>
+  </si>
+  <si>
+    <t>Data processing</t>
+  </si>
+  <si>
+    <t>Platform ID (list)</t>
+  </si>
+  <si>
+    <t>SRA Study ID (raw data)</t>
+  </si>
+  <si>
+    <t>BioSample/BioProject ID</t>
+  </si>
+  <si>
+    <t>File types/resources provided (list)</t>
+  </si>
+  <si>
+    <t>Submission date</t>
+  </si>
+  <si>
+    <t>Last update date</t>
+  </si>
+  <si>
+    <t>Organization name</t>
+  </si>
+  <si>
+    <t>Contact name</t>
+  </si>
+  <si>
+    <t>E-mail(s)</t>
+  </si>
+  <si>
+    <t>Country</t>
+  </si>
+  <si>
+    <t>PMID</t>
+  </si>
+  <si>
+    <t>PMCID</t>
+  </si>
+  <si>
+    <t>DOI</t>
+  </si>
+  <si>
+    <t>GSE185119</t>
+  </si>
+  <si>
+    <t>Expression profiling by high throughput sequencing</t>
+  </si>
+  <si>
+    <t>Gene expression profiling of trophoblastic organoid from the placental villi of intrauterine and tubal ectopic pregnancies</t>
+  </si>
+  <si>
+    <t>Homo sapiens</t>
+  </si>
+  <si>
+    <t>tissue: placenta | geatational days: 49 | maternal age: 36 | cell type: trophoblastic organoid | passages: P3 | geatational days: 52 | maternal age: 20 | geatational days: 46 | maternal age: 42 | geatational days: 53 | maternal age: 26 | geatational days: 45 | maternal age: 33 | passages: P2 | geatational days: 50 | maternal age: 27 | geatational days: 54 | maternal age: 32 | maternal age: 31 | maternal age: 28 | passages: P4</t>
+  </si>
+  <si>
+    <t>total RNA</t>
+  </si>
+  <si>
+    <t>placental villi were removed, digested, then the trophoblastic organoids were cultured, and RNA was harvested using Trizol reagent. NEBNext® Ultra™ RNA Library Prep Kit for Illumina® (#E7530L, NEB, USA) was used with 2 ug of total RNA for the construction of sequencing libraries. RNA libraries were prepared for sequencing using standard Illumina protocols</t>
+  </si>
+  <si>
+    <t>RNA-Seq</t>
+  </si>
+  <si>
+    <t>transcriptomic</t>
+  </si>
+  <si>
+    <t>cDNA</t>
+  </si>
+  <si>
+    <t>Illumina HiSeq 4000</t>
+  </si>
+  <si>
+    <t>RNA-seq was performed on trophonblastic organoid from pregnant women at 6-8 gestational weeks. Exclusion criteria for all samples are: IP with EP histories, miscarriage, preeclampsia, and preterm delivery. EP with some risk factors associated with fallopian tubal abnormalities, e.g., smoking, obvious tubal inflammatory adhesions, previous fallopian tubal diseases, and tubal surgery histories, were also excluded for avoiding complications. In each case, gestational days was 40-64 days confirmed from the last menstrual period. n=5 for both IP and TEP.</t>
+  </si>
+  <si>
+    <t>GPL20301</t>
+  </si>
+  <si>
+    <t>SRP339552</t>
+  </si>
+  <si>
+    <t>PRJNA767678</t>
+  </si>
+  <si>
+    <t>gz</t>
+  </si>
+  <si>
+    <t>09/30/2021</t>
+  </si>
+  <si>
+    <t>09/02/2024</t>
+  </si>
+  <si>
+    <t>School of Medicine, Shanghai Jiaotong University</t>
+  </si>
+  <si>
+    <t>Xiaoya Zhao</t>
+  </si>
+  <si>
+    <t>zhaoxiaoya@sjtu.edu.cn</t>
+  </si>
+  <si>
+    <t>China</t>
+  </si>
+  <si>
+    <t>GSE214007</t>
+  </si>
+  <si>
+    <t>The Transcriptome Analysis Reveals the Underlying Mechanism of Low Fetal Weight due to Prenatal High Estradiol Exposure in Mice</t>
+  </si>
+  <si>
+    <t>Mus musculus</t>
+  </si>
+  <si>
+    <t>tissue: placenta | Sex: female | treatment: normal control | Sex: male | treatment: high E2 prenatal exposure</t>
+  </si>
+  <si>
+    <t>Three male and three female placenta samples per group were randomly selected for RNA isolation, which was performed by using TRIzol Reagent (Invitrogen) under the manufacturer’s instructions. Extracted RNA was dissolved in RNase-free water and quantified using Qubit○R RNA Assay Kit in Qubit○R 2.0 Flurometer (Life Technologies, CA, USA). RNA integrity was assessed using the RNA Nano 6000 Assay Kit of the Bioanalyzer 2100 system (Agilent Technologies, CA, USA). A total amount of 3 μg RNA per sample was used as input material for RNA sample preparations. Sequencing libraries were generated using NEBXext○R UltraTM RNA Library Prep Kit for Illumina○R (NEB, USA) following manufacturer’s recommendations and index codes were added to attribute sequences to each sample. Briefly, mRNA was purified from total RNA using poly-T oligo-attached magnetic beads. Fragmentation was carried out using divalent cations under elevated temperature in NEBNest First Strand Synthesis Reaction Buffer (5×). First strand cDNA was synthesized using random hexamer primer and M-MuLV Reverse Transcriptase (RNase H). Second strand cDNA synthesis was subsequently performed using DNA Polymerase I and RNase H. Remaining overhangs were converted into blunt ends via exonuclease/polymerase activities. After adenylation of 3’ ends of DNA fragments, NEBNext Adaptor with hairpin loop structure were ligated to prepare for hybridization. In order to select cDNA fragments of preferentially 250~300 bp in length, the library fragments were purified with AMPure XP system (Beckman Coulter, Beverly, USA). Then 3 μl USER Enzyme (NEB, USA) was used with size-selected, adaptor-ligated cDNA at 37℃ for 15 min followed by 5 min at 95℃ before PCR. Then PCR was performed with Phusion High-Fidelity DNA polymerase, Universal PCR primers and Index (X) Primer. At last, PCR products were purified (AMPure XP system) and library quality was assessed on the Agilent bioanalyzer 2100 system.</t>
+  </si>
+  <si>
+    <t>HiSeq X Ten</t>
+  </si>
+  <si>
+    <t>Comparative gene expression profiling analysis of RNA-seq data for 12 samples including 3 placentas derived from male pups and 3 placentas obtained from female pups in both control and E2-treated groups.</t>
+  </si>
+  <si>
+    <t>GPL21273</t>
+  </si>
+  <si>
+    <t>PRJNA883619</t>
+  </si>
+  <si>
+    <t>09/23/2022</t>
+  </si>
+  <si>
+    <t>09/01/2024</t>
+  </si>
+  <si>
+    <t>Shanghai Jiaotong University</t>
+  </si>
+  <si>
+    <t>Xiaoguo Zheng</t>
+  </si>
+  <si>
+    <t>zxg@sagc.org.cn</t>
+  </si>
+  <si>
+    <t>GSE272695</t>
+  </si>
+  <si>
+    <t>Decidual natural killer cells promote extravillus trophoblast developmental pathways: evidence from trophoblast organoid co-cultures</t>
+  </si>
+  <si>
+    <t>tissue: placenta | cell line: Org_W_6.2_A | cell type: trophoblast | genotype: NA | treatment: whole | batch: 2 | tissue: placenta_decidua | cell line: OrgNK_W_6.1_4 | cell type: trophoblast_dNK | cell line: OrgNK_S_6.1_4 | treatment: sorted | cell line: OrgNK_W_6.2_6.1 | cell line: Org_S_6.1_A | batch: 1 | cell line: OrgNK_S_6.2_6.1 | tissue: decidua | cell line: NK_W_A_4 | cell type: dNK | cell line: NK_W_A_6.1 | cell line: OrgNK_W_6.1_6.1 | cell line: Org_W_6.1_A | cell line: OrgNK_W_6.2_4</t>
+  </si>
+  <si>
+    <t>polyA RNA</t>
+  </si>
+  <si>
+    <t>All samples were collected and snap frozen following seven days of culture, then processed according to the manufacturer’s instructions using the RNeasy Micro Kit (Qiagen 74004) for total RNA isolation. The sample disruption and homogenization steps were performed using QIAShredders (Qiagen 79654). Libraries were prepared at the Donnelley Centre at the University of Toronto using Takara SMART-Seq v.4 Ultra Low Input RNA kits.</t>
+  </si>
+  <si>
+    <t>Illumina NovaSeq X</t>
+  </si>
+  <si>
+    <t>organoids grown under maintenance conditions in the presence or absence of decidual natural killer cells from allogenic donors</t>
+  </si>
+  <si>
+    <t>GPL34281</t>
+  </si>
+  <si>
+    <t>PRJNA1137979</t>
+  </si>
+  <si>
+    <t>07/19/2024</t>
+  </si>
+  <si>
+    <t>08/31/2024</t>
+  </si>
+  <si>
+    <t>University of Toronto</t>
+  </si>
+  <si>
+    <t>Brian Joseph Cox</t>
+  </si>
+  <si>
+    <t>b.cox@utoronto.ca</t>
+  </si>
+  <si>
+    <t>Canada</t>
+  </si>
+  <si>
+    <t>GSE247712</t>
+  </si>
+  <si>
+    <t>Genome binding/occupancy profiling by high throughput sequencing, Expression profiling by high throughput sequencing</t>
+  </si>
+  <si>
+    <t>GSE247709, GSE247711</t>
+  </si>
+  <si>
+    <t>Distinct roles of SOX9 in self-renewal of progenitors and mesenchymal transition of the endothelium</t>
+  </si>
+  <si>
+    <t>tissue: placenta | cell type: Endothelial colony-forming cells | treatment: oxLDL(25ug/ul) 5 days | treatment: vehicle 5 days</t>
+  </si>
+  <si>
+    <t>genomic DNA, total RNA</t>
+  </si>
+  <si>
+    <t>50,000 ECFCs were trypsinized and washed twice in cold PBS. Pelleted cells were lysed and then directly transposed using the TDE1 DNA Enzyme and Buffer kit (Illumina, CA, US). The transposition reaction was completed with thermomixing at 37°C for 30 minutes at 300 rpm. Transposed DNA was purified with MinElute column cleanup (Qiagen, Valencia, CA) Prepared libraries were purified with MinElute column clean-up (Qiagen). The ATAC-seq library pool was quantified on the Agilent Bioanalyzer with the High Sensitivity DNA kit (Agilent Technologies, 4067-4626). Sequencing was performed using the Illumina NextSeq500 (NextSeq control software v4.0.0 / Real Time Analysis v2.11.3). The library pool was diluted and denatured according to the standard NextSeq protocol (Document # 15048776 v16) and sequenced to generate paired-end 76 bp reads using a 150 cycle NextSeq500/550 Mid Output reagent Kit v2.5 (Illumina, 20024904). After sequencing, fastq files were generated using bcl2fastq2 (v2.20.0.422).
+RNA was extracted using Rneasy mini plus kit (Qiagen) RNA-Seq libraries were prepared using the Illumina stranded total RNA prep ligation with Ribo-Zero plus kit (Illumina, 20040529) and IDT for Illumina RNA UD Indexes (Illumina, 20040553/20040554/20040555/20040556) according to the standard manufacturer’s protocol (Illumina, Document # 1000000124514 v01).The libraries were quantified on the Perkin Elmer LabChip GX Touch with the DNA High Sensitivity Reagent kit (Perkin Elmer, CLS760672). Libraries were pooled in equimolar ratios, and the pool was quantified by qPCR using the KAPA Library Quantification Kit – Illumina/Universal (KAPA Biosystems, KK4824) in combination with the Life Technologies Viia 7 real time PCR instrument.</t>
+  </si>
+  <si>
+    <t>ATAC-seq, RNA-Seq</t>
+  </si>
+  <si>
+    <t>genomic, transcriptomic</t>
+  </si>
+  <si>
+    <t>other, cDNA</t>
+  </si>
+  <si>
+    <t>Illumina NextSeq 500</t>
+  </si>
+  <si>
+    <t>Refer to individual Series</t>
+  </si>
+  <si>
+    <t>GPL18573</t>
+  </si>
+  <si>
+    <t>PRJNA1040198</t>
+  </si>
+  <si>
+    <t>tar</t>
+  </si>
+  <si>
+    <t>11/14/2023</t>
+  </si>
+  <si>
+    <t>The University of Queensland Diamantina Institute</t>
+  </si>
+  <si>
+    <t>laura sormani</t>
+  </si>
+  <si>
+    <t>l.sormani@uq.edu.au, sormani.lau@gmail.com</t>
+  </si>
+  <si>
+    <t>Australia</t>
+  </si>
+  <si>
+    <t>38733496</t>
+  </si>
+  <si>
+    <t>PMC11303482</t>
+  </si>
+  <si>
+    <t>10.1007/s10456-024-09927-7</t>
+  </si>
+  <si>
+    <t>GSE247711</t>
+  </si>
+  <si>
+    <t>Distinct roles of SOX9 in self-renewal of progenitors and mesenchymal transition of the endothelium [RNA-seq]</t>
+  </si>
+  <si>
+    <t>tissue: placenta | cell type: Endothelial colony-forming cells | treatment: vehicle 5 days | treatment: oxLDL(25ug/ul) 5 days</t>
+  </si>
+  <si>
+    <t>RNA was extracted using Rneasy mini plus kit (Qiagen) RNA-Seq libraries were prepared using the Illumina stranded total RNA prep ligation with Ribo-Zero plus kit (Illumina, 20040529) and IDT for Illumina RNA UD Indexes (Illumina, 20040553/20040554/20040555/20040556) according to the standard manufacturer’s protocol (Illumina, Document # 1000000124514 v01).The libraries were quantified on the Perkin Elmer LabChip GX Touch with the DNA High Sensitivity Reagent kit (Perkin Elmer, CLS760672). Libraries were pooled in equimolar ratios, and the pool was quantified by qPCR using the KAPA Library Quantification Kit – Illumina/Universal (KAPA Biosystems, KK4824) in combination with the Life Technologies Viia 7 real time PCR instrument.</t>
+  </si>
+  <si>
+    <t>RNA-sequencing of endothelial colony-forming cells (ECFCs; 4 donors per group) treated with oxLDL (25ug/ul)or vehicle for 5 days.</t>
+  </si>
+  <si>
+    <t>PRJNA1040200</t>
+  </si>
+  <si>
+    <t>08/30/2024</t>
+  </si>
+  <si>
+    <t>GSE230783</t>
+  </si>
+  <si>
+    <t>Extracellular Vesicle contents of mouse trophoblast cells and their predicted influence on fetal brain development</t>
+  </si>
+  <si>
+    <t>cell line: Mouse Neural Cortical Stem Cells | cell type: Neural stem cell | genotype: WT | treatment: No treatment given | treatment: Incubated with EVs from mTSCs for ~ 24 hours | treatment: Incubated with EVs from pTGCs for ~24 hours</t>
+  </si>
+  <si>
+    <t>RNA was harvested using Rneasy mini plus kit (Qiagen). 500ng of total RNA was used for the construction of sequencing libraries. RNA libraries for RNA-seq were prepared using the Illumina Stranded mRNA Library Prep Kit following manufacturer's protocols.</t>
+  </si>
+  <si>
+    <t>Illumina NovaSeq 6000</t>
+  </si>
+  <si>
+    <t>Four replicates each for three different treatments, total of 12 samples and 3 conditions (1 control).</t>
+  </si>
+  <si>
+    <t>GPL24247</t>
+  </si>
+  <si>
+    <t>PRJNA962560</t>
+  </si>
+  <si>
+    <t>04/27/2023</t>
+  </si>
+  <si>
+    <t>08/28/2024</t>
+  </si>
+  <si>
+    <t>Iowa State University</t>
+  </si>
+  <si>
+    <t>Geetu Tuteja</t>
+  </si>
+  <si>
+    <t>arnstrm@iastate.edu, geetu@iastate.edu</t>
+  </si>
+  <si>
+    <t>USA</t>
+  </si>
+  <si>
+    <t>37883444</t>
+  </si>
+  <si>
+    <t>PMC10873279</t>
+  </si>
+  <si>
+    <t>10.1093/biolre/ioad146</t>
+  </si>
+  <si>
+    <t>GSE232526</t>
+  </si>
+  <si>
+    <t>Regenerative trophoblast models are largely in concordance with trophoblasts from peri-implantation human embryos while maintaining subtle differences</t>
+  </si>
+  <si>
+    <t>cell type: Trophoblasts | treatment: Differentiated | treatment: BAP | treatment: undifferentiated | cell type: Embryonic stem cells | treatment: Control</t>
+  </si>
+  <si>
+    <t>RNA isolation from cultured cells was used Trizol reagent. RNA-seq libraries were prepared using the NEBNext RNA Library Prep Kit (New England Biolabs, NEB) .</t>
+  </si>
+  <si>
+    <t>We collected human TSC and TSC derived STB and EVT, as well as hESC derived trophoblast cells (separated by cell size, &lt;40um and &gt;70um) by BAP treatment, then total RNA was extracted, followed by RNA-sequencing analysis.</t>
+  </si>
+  <si>
+    <t>GPL24676</t>
+  </si>
+  <si>
+    <t>PRJNA972666</t>
+  </si>
+  <si>
+    <t>05/15/2023</t>
+  </si>
+  <si>
+    <t>08/21/2024</t>
+  </si>
+  <si>
+    <t>University of Florida</t>
+  </si>
+  <si>
+    <t>Zongliang Jiang</t>
+  </si>
+  <si>
+    <t>z.jiang1@ufl.edu</t>
+  </si>
+  <si>
+    <t>39109839</t>
+  </si>
+  <si>
+    <t>GSE270174</t>
+  </si>
+  <si>
+    <t>Expression profiling by high throughput sequencing, Other</t>
+  </si>
+  <si>
+    <t>GSE270170, GSE270173, GSE298474</t>
+  </si>
+  <si>
+    <t>Trajectory modeling of first trimester placenta highlight differences between cytotrophoblast progenitors and trophoblast stem cells</t>
+  </si>
+  <si>
+    <t>tissue: whole placenta | gestational age_(weeksdays): 8w4d | gestational age_(weeksdays): 6w5d | gestational age_(weeksdays): 12w2d | gestational age_(weeksdays): 13w0d | tissue: Basal Plate placenta | tissue: chorionic plate placenta | gestational age_(weeksdays): 6w2d | cell line: TSC_906 | gestational age_(weeksdays): 5w5d | cell line: TSC_1000 | gestational age_(weeksdays): 6w3d | cell line: TSC_1278 | gestational age_(weeksdays): 6w4d | cell type: CP_CTB | placenta block: 1459 | roi number: 2 | area: 14449.158421 | nucleicount: 236 | roicoordinatex: 40196 | roicoordinatey: 26505 | rawreads: 1341272 | alignedreads: 1287538 | deduplicatedreads: 534350 | trimmedreads: 1335490 | stitchedreads: 1332134 | sequencingsaturation: 58.4983122828219 | treatment: stained for EGFR and HLA-g | roi number: 4 | area: 15342.156068 | nucleicount: 300 | roicoordinatex: 31926 | roicoordinatey: 33007 | rawreads: 2760801 | alignedreads: 2654631 | deduplicatedreads: 1208839 | trimmedreads: 2748041 | stitchedreads: 2739557 | sequencingsaturation: 54.4630119967709 | roi number: 5 | area: 12043.897629 | nucleicount: 244 | roicoordinatex: 32398 | roicoordinatey: 29230 | rawreads: 1701103 | alignedreads: 1637411 | deduplicatedreads: 750443 | trimmedreads: 1695244 | stitchedreads: 1690827 | sequencingsaturation: 54.1689288761343 | roi number: 6 | area: 9469.674201 | nucleicount: 207 | roicoordinatex: 29988 | roicoordinatey: 29510 | rawreads: 2076755 | alignedreads: 1976138 | deduplicatedreads: 795007 | trimmedreads: 2045813 | stitchedreads: 2039914 | sequencingsaturation: 59.7696618353577 | roi number: 7 | area: 10989.862422 | nucleicount: 175 | roicoordinatex: 28903 | roicoordinatey: 28508 | rawreads: 1640999 | alignedreads: 1575649 | deduplicatedreads: 696240 | trimmedreads: 1631308 | stitchedreads: 1626593 | sequencingsaturation: 55.8124937724074 | roi number: 8 | area: 14612.732005 | nucleicount: 296 | roicoordinatex: 28442 | roicoordinatey: 27334 | rawreads: 1950452 | alignedreads: 1874730 | deduplicatedreads: 833323 | trimmedreads: 1940815 | stitchedreads: 1934521 | sequencingsaturation: 55.5497058243054 | cell type: BP_CTB | roi number: 10 | area: 15199.029182 | nucleicount: 274 | roicoordinatex: 25231 | roicoordinatey: 28257 | rawreads: 2630155 | alignedreads: 2528174 | deduplicatedreads: 1122684 | trimmedreads: 2618367 | stitchedreads: 2610548 | sequencingsaturation: 55.5930881339655 | roi number: 11 | area: 11334.920264 | roicoordinatex: 35544 | roicoordinatey: 34813 | rawreads: 2187239 | alignedreads: 2091924 | deduplicatedreads: 922281 | trimmedreads: 2170409 | stitchedreads: 2162998 | sequencingsaturation: 55.9123084777458 | roi number: 12 | area: 9244.44352 | nucleicount: 137 | roicoordinatex: 37210 | roicoordinatey: 35477 | rawreads: 2835282 | alignedreads: 2718475 | deduplicatedreads: 1064762 | trimmedreads: 2825486 | stitchedreads: 2816046 | sequencingsaturation: 60.8323784474752 | roi number: 15 | area: 12260.093723 | nucleicount: 288 | roicoordinatex: 33653 | roicoordinatey: 45026 | rawreads: 2664547 | alignedreads: 2561155 | deduplicatedreads: 1020136 | trimmedreads: 2656080 | stitchedreads: 2649022 | sequencingsaturation: 60.168908168385 | placenta block: 1347 | roi number: 1 | area: 11350.770417 | nucleicount: 196 | roicoordinatex: 16137 | roicoordinatey: 38952 | rawreads: 2740882 | alignedreads: 2631371 | deduplicatedreads: 1085994 | trimmedreads: 2730958 | stitchedreads: 2723162 | sequencingsaturation: 58.7289667629536 | area: 9144.904556 | nucleicount: 189 | roicoordinatex: 15658 | roicoordinatey: 44495 | rawreads: 1890326 | alignedreads: 1810293 | deduplicatedreads: 828488 | trimmedreads: 1878337 | stitchedreads: 1873554 | sequencingsaturation: 54.2345907540934 | roi number: 3 | area: 17862.964479 | nucleicount: 304 | roicoordinatex: 12221 | roicoordinatey: 51340 | rawreads: 3478854 | alignedreads: 3346869 | deduplicatedreads: 1410762 | trimmedreads: 3464633 | stitchedreads: 3453900 | sequencingsaturation: 57.8483053863178 | area: 12154.056196 | nucleicount: 219 | roicoordinatex: 11501 | roicoordinatey: 51747 | rawreads: 3820744 | alignedreads: 3665784 | deduplicatedreads: 1645748 | trimmedreads: 3802864 | stitchedreads: 3791256 | sequencingsaturation: 55.1051562230617 | area: 9685.553292 | nucleicount: 184 | roicoordinatex: 9666 | roicoordinatey: 51237 | rawreads: 2338198 | alignedreads: 2244783 | deduplicatedreads: 970300 | trimmedreads: 2328742 | stitchedreads: 2323128 | sequencingsaturation: 56.7753319585902 | area: 10009.054924 | nucleicount: 260 | roicoordinatex: 9022 | roicoordinatey: 53712 | rawreads: 1846262 | alignedreads: 1751522 | deduplicatedreads: 733393 | trimmedreads: 1824223 | stitchedreads: 1818695 | sequencingsaturation: 58.1282450348897 | area: 15345.326099 | nucleicount: 212 | roicoordinatex: 18802 | roicoordinatey: 45486 | rawreads: 3584120 | alignedreads: 3438143 | deduplicatedreads: 1477202 | trimmedreads: 3571218 | stitchedreads: 3560617 | sequencingsaturation: 57.0348877286372 | area: 13574.229948 | nucleicount: 210 | roicoordinatex: 17838 | roicoordinatey: 34306 | rawreads: 3650049 | alignedreads: 3502298 | deduplicatedreads: 1294079 | trimmedreads: 3638442 | stitchedreads: 3626867 | sequencingsaturation: 63.0505742229816 | placenta block: 1344 | area: 27350.390852 | nucleicount: 318 | roicoordinatex: 21883 | roicoordinatey: 37372 | rawreads: 4770734 | alignedreads: 4524626 | deduplicatedreads: 1997351 | trimmedreads: 4754774 | stitchedreads: 4741023 | sequencingsaturation: 55.8559978216984 | area: 26421.413356 | nucleicount: 371 | roicoordinatex: 23171 | roicoordinatey: 34666 | rawreads: 7029453 | alignedreads: 6735046 | deduplicatedreads: 2837921 | trimmedreads: 7003523 | stitchedreads: 6983261 | sequencingsaturation: 57.8633761372974 | area: 29831.098374 | nucleicount: 389 | roicoordinatex: 22954 | roicoordinatey: 35946 | rawreads: 3763805 | alignedreads: 3563109 | deduplicatedreads: 1568591 | trimmedreads: 3746950 | stitchedreads: 3733966 | sequencingsaturation: 55.9769010715081 | area: 26601.312598 | nucleicount: 302 | roicoordinatex: 28437 | roicoordinatey: 25504 | rawreads: 5376639 | alignedreads: 5173625 | deduplicatedreads: 2177877 | trimmedreads: 5355807 | stitchedreads: 5338582 | sequencingsaturation: 57.9042354248714 | area: 17046.047568 | nucleicount: 243 | roicoordinatex: 29401 | roicoordinatey: 23483 | rawreads: 1786754 | alignedreads: 1702991 | deduplicatedreads: 747091 | trimmedreads: 1775162 | stitchedreads: 1769780 | sequencingsaturation: 56.1306548302369 | area: 19586.827172 | nucleicount: 227 | roicoordinatex: 35614 | roicoordinatey: 29731 | rawreads: 5282030 | alignedreads: 5072755 | deduplicatedreads: 2013849 | trimmedreads: 5262605 | stitchedreads: 5248361 | sequencingsaturation: 60.3006847364006 | area: 27875.347936 | nucleicount: 305 | roicoordinatex: 34956 | roicoordinatey: 30689 | rawreads: 5684446 | alignedreads: 5446502 | deduplicatedreads: 2352892 | trimmedreads: 5642965 | stitchedreads: 5628226 | sequencingsaturation: 56.7999424217599 | area: 24112.362996 | nucleicount: 358 | roicoordinatex: 30310 | roicoordinatey: 33671 | rawreads: 9464378 | alignedreads: 9074215 | deduplicatedreads: 3449071 | trimmedreads: 9432236 | stitchedreads: 9408289 | sequencingsaturation: 61.9904201079653 | area: 23180.849476 | nucleicount: 347 | roicoordinatex: 22684 | roicoordinatey: 47025 | rawreads: 3609616 | alignedreads: 3466874 | deduplicatedreads: 1892760 | trimmedreads: 3596742 | stitchedreads: 3585891 | sequencingsaturation: 45.4044190818588 | area: 26203.315244 | nucleicount: 340 | roicoordinatex: 26230 | roicoordinatey: 46475 | rawreads: 8876662 | alignedreads: 8535019 | deduplicatedreads: 3601275 | trimmedreads: 8848121 | stitchedreads: 8823191 | sequencingsaturation: 57.8058935779756 | area: 20514.061151 | nucleicount: 353 | roicoordinatex: 32123 | roicoordinatey: 43050 | rawreads: 5419551 | alignedreads: 5210592 | deduplicatedreads: 2249592 | trimmedreads: 5401818 | stitchedreads: 5384169 | sequencingsaturation: 56.8265563682591 | gestational age_(weeksdays): 8w3d | gestational age_(weeksdays): 8w1d | cell line: TSC_1815 | cell line: TSC_1816</t>
+  </si>
+  <si>
+    <t>Single cell suspensions were washed, filtered for cell debris, counted, and stained with a viability marker to ensure correct loading concentration and a high percentage of live cells. Cell suspensions were then loaded onto the 10x Genomics Controller for GEM generation. Library was performed according to the manufacturer’s instructions (single cell 3’ v2 protocol, 10x Genomics). Briefly, GCs were resuspended in the master mix and loaded together with partitioning oil and gel beads into the chip to generate the gel bead-in-emulsion (GEM). The poly-A RNA from the cell lysate contained in every single GEM was retrotranscripted to cDNA, which contains an Ilumina R1 primer sequence, Unique Molecular Identifier (UMI) and the 10x Barcode. The pooled barcoded cDNA was then cleaned up with Silane DynaBeads, amplified by PCR and the apropiated sized fragments were selected with SPRIselect reagent for subsequent library construction. During the library construction Ilumina R2 primer sequence, paired-end constructs with P5 and P7 sequences and a sample index were added.
+Sections were deparaffinized and incubated overnight with the Whole Transcriptomic Assay UV-cleavable biological probes according to manufacturer’s instructions. Samples were stained with CONFIRM® anti-EGFR (5B7) Rabbit Monoclonal Primary Antibody (Ventana #790-4347, 1:20 dilution) and anti-HLA-G (4H48) mouse primary antibody (Abcam #ab52455, 1:1000 dilution) for 2 hours followed by secondary staining for 1h with Alexa Fluor anti-rabbit-647 (Life Technologies, 1:500 dilution), Alexa Fluor anti-mouse-594 (Life Technologies, 1:500 dilution), and SYTO13 (Nanostring, 1:10 dilution) for nuclei staining. Slides were scanned on a GeoMx digital spatial profiler machine r. Based on the morphology markers, areas of interest (AOIs) containing at least EGFR+/HLA-G- 100 nuclei were manually selected. Spatial transcriptomic libraries were prepared with GeoMx reagents according to the manufacturer’s protocol - Direct PCR</t>
+  </si>
+  <si>
+    <t>RNA-Seq, OTHER</t>
+  </si>
+  <si>
+    <t>transcriptomic single cell, transcriptomic</t>
+  </si>
+  <si>
+    <t>cDNA, other</t>
+  </si>
+  <si>
+    <t>PRJNA1125375</t>
+  </si>
+  <si>
+    <t>06/18/2024</t>
+  </si>
+  <si>
+    <t>05/31/2025</t>
+  </si>
+  <si>
+    <t>UCSD</t>
+  </si>
+  <si>
+    <t>Robert E Morey</t>
+  </si>
+  <si>
+    <t>robmoreyucsd@gmail.com, remorey@health.ucsd.edu</t>
+  </si>
+  <si>
+    <t>39071344</t>
+  </si>
+  <si>
+    <t>PMC11275976</t>
+  </si>
+  <si>
+    <t>10.1101/2024.07.12.603155</t>
+  </si>
+  <si>
+    <t>GSE270170</t>
+  </si>
+  <si>
+    <t>Trajectory modeling of first trimester placenta highlight differences between cytotrophoblast progenitors and trophoblast stem cells [scRNA-seq]</t>
+  </si>
+  <si>
+    <t>tissue: whole placenta | gestational age_(weeksdays): 8w4d | gestational age_(weeksdays): 6w5d | gestational age_(weeksdays): 12w2d | gestational age_(weeksdays): 13w0d | tissue: Basal Plate placenta | tissue: chorionic plate placenta | gestational age_(weeksdays): 6w2d | cell line: TSC_906 | gestational age_(weeksdays): 5w5d | cell line: TSC_1000 | gestational age_(weeksdays): 6w3d | cell line: TSC_1278 | gestational age_(weeksdays): 6w4d</t>
+  </si>
+  <si>
+    <t>Single cell suspensions were washed, filtered for cell debris, counted, and stained with a viability marker to ensure correct loading concentration and a high percentage of live cells. Cell suspensions were then loaded onto the 10x Genomics Controller for GEM generation. Library was performed according to the manufacturer’s instructions (single cell 3’ v2 protocol, 10x Genomics). Briefly, GCs were resuspended in the master mix and loaded together with partitioning oil and gel beads into the chip to generate the gel bead-in-emulsion (GEM). The poly-A RNA from the cell lysate contained in every single GEM was retrotranscripted to cDNA, which contains an Ilumina R1 primer sequence, Unique Molecular Identifier (UMI) and the 10x Barcode. The pooled barcoded cDNA was then cleaned up with Silane DynaBeads, amplified by PCR and the apropiated sized fragments were selected with SPRIselect reagent for subsequent library construction. During the library construction Ilumina R2 primer sequence, paired-end constructs with P5 and P7 sequences and a sample index were added.</t>
+  </si>
+  <si>
+    <t>transcriptomic single cell</t>
+  </si>
+  <si>
+    <t>For whole placental samples, chorionic villi were minced and subjected to three sequential enzymatic digestions. After filtration, cells were counted and loaded on the 10x Genomics chip. For basal and chorion samples, under a microscope we collected the tips (basal fraction) and the base (chorionic fraction) of the villi while the middle section was discarded. The two fractions were subjected to the same sequential enzymatic digestion and after filtration cells were separated on a Percoll (Sigma-Aldrich) gradient.</t>
+  </si>
+  <si>
+    <t>PRJNA1125368</t>
+  </si>
+  <si>
+    <t>08/17/2024</t>
+  </si>
+  <si>
+    <t>GSE232692</t>
+  </si>
+  <si>
+    <t>Rapid retinoic acid-induced trophectoderm model from human induced pluripotent stem cells</t>
+  </si>
+  <si>
+    <t>tissue: cell line | cell line: iPS(IMR90)-4 | cell type: induced pluripotent stem cells | genotype: WT | treatment: trophectoderm differentiation</t>
+  </si>
+  <si>
+    <t>Cell pellets were collected and lysed using QiaShredder columns (Qiagen). RNA was isolated using the RNeasy Mini Kit (Qiagen) as the manufacturer recommends, including incubation with DNase I (RNAse-free DNase Set, Qiagen). RNA libraries for RNA-seq were prepared using TruSeq Stranded mRNA (Illumina).</t>
+  </si>
+  <si>
+    <t>Gene expression profiling analysis of RNA-seq data from IMR90-4 iPS cells during differentiation toward trophoectoderm. Samples were collected from days 0, 1, 3, and  5 of the differentiation in duplicate.</t>
+  </si>
+  <si>
+    <t>PRJNA973592</t>
+  </si>
+  <si>
+    <t>05/17/2023</t>
+  </si>
+  <si>
+    <t>08/15/2024</t>
+  </si>
+  <si>
+    <t>University of Minnesota</t>
+  </si>
+  <si>
+    <t>Samira Azarin</t>
+  </si>
+  <si>
+    <t>39107470</t>
+  </si>
+  <si>
+    <t>PMC11303561</t>
+  </si>
+  <si>
+    <t>10.1038/s41598-024-68952-0</t>
+  </si>
+  <si>
+    <t>Failed_GSE_IDs</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -64,13 +614,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -108,7 +666,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -142,6 +700,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -176,9 +735,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -351,171 +911,929 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:AB12"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="19" max="19" width="46.28515625" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1"/>
+    <row r="1" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB1" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D2">
+        <v>9</v>
+      </c>
+      <c r="E2" t="s">
+        <v>30</v>
+      </c>
+      <c r="F2" t="s">
+        <v>31</v>
+      </c>
+      <c r="G2" t="s">
+        <v>32</v>
+      </c>
+      <c r="H2" t="s">
+        <v>33</v>
+      </c>
+      <c r="I2" t="s">
+        <v>34</v>
+      </c>
+      <c r="J2" t="s">
+        <v>35</v>
+      </c>
+      <c r="K2" t="s">
+        <v>36</v>
+      </c>
+      <c r="L2" t="s">
+        <v>37</v>
+      </c>
+      <c r="M2" t="s">
+        <v>38</v>
+      </c>
+      <c r="N2" t="s">
+        <v>39</v>
+      </c>
+      <c r="P2" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>41</v>
+      </c>
+      <c r="R2" t="s">
+        <v>42</v>
+      </c>
+      <c r="S2" t="s">
+        <v>43</v>
+      </c>
+      <c r="T2" t="s">
+        <v>44</v>
+      </c>
+      <c r="U2" t="s">
+        <v>45</v>
+      </c>
+      <c r="V2" t="s">
+        <v>46</v>
+      </c>
+      <c r="W2" t="s">
+        <v>47</v>
+      </c>
+      <c r="X2" t="s">
+        <v>48</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="3" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>50</v>
+      </c>
+      <c r="B3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D3">
+        <v>12</v>
+      </c>
+      <c r="E3" t="s">
+        <v>51</v>
+      </c>
+      <c r="F3" t="s">
+        <v>52</v>
+      </c>
+      <c r="G3" t="s">
+        <v>53</v>
+      </c>
+      <c r="H3" t="s">
+        <v>33</v>
+      </c>
+      <c r="I3" t="s">
+        <v>54</v>
+      </c>
+      <c r="J3" t="s">
+        <v>35</v>
+      </c>
+      <c r="K3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M3" t="s">
+        <v>55</v>
+      </c>
+      <c r="N3" t="s">
+        <v>56</v>
+      </c>
+      <c r="P3" t="s">
+        <v>57</v>
+      </c>
+      <c r="R3" t="s">
+        <v>58</v>
+      </c>
+      <c r="S3" t="s">
+        <v>43</v>
+      </c>
+      <c r="T3" t="s">
+        <v>59</v>
+      </c>
+      <c r="U3" t="s">
+        <v>60</v>
+      </c>
+      <c r="V3" t="s">
+        <v>61</v>
+      </c>
+      <c r="W3" t="s">
+        <v>62</v>
+      </c>
+      <c r="X3" t="s">
+        <v>63</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="4" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>50</v>
+      </c>
+      <c r="B4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D4">
+        <v>12</v>
+      </c>
+      <c r="E4" t="s">
+        <v>51</v>
+      </c>
+      <c r="F4" t="s">
+        <v>52</v>
+      </c>
+      <c r="G4" t="s">
+        <v>53</v>
+      </c>
+      <c r="H4" t="s">
+        <v>33</v>
+      </c>
+      <c r="I4" t="s">
+        <v>54</v>
+      </c>
+      <c r="J4" t="s">
+        <v>35</v>
+      </c>
+      <c r="K4" t="s">
+        <v>36</v>
+      </c>
+      <c r="L4" t="s">
+        <v>37</v>
+      </c>
+      <c r="M4" t="s">
+        <v>55</v>
+      </c>
+      <c r="N4" t="s">
+        <v>56</v>
+      </c>
+      <c r="P4" t="s">
+        <v>57</v>
+      </c>
+      <c r="R4" t="s">
+        <v>58</v>
+      </c>
+      <c r="S4" t="s">
+        <v>43</v>
+      </c>
+      <c r="T4" t="s">
+        <v>59</v>
+      </c>
+      <c r="U4" t="s">
+        <v>60</v>
+      </c>
+      <c r="V4" t="s">
+        <v>61</v>
+      </c>
+      <c r="W4" t="s">
+        <v>62</v>
+      </c>
+      <c r="X4" t="s">
+        <v>63</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="5" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>64</v>
+      </c>
+      <c r="B5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D5">
+        <v>11</v>
+      </c>
+      <c r="E5" t="s">
+        <v>65</v>
+      </c>
+      <c r="F5" t="s">
+        <v>31</v>
+      </c>
+      <c r="G5" t="s">
+        <v>66</v>
+      </c>
+      <c r="H5" t="s">
+        <v>67</v>
+      </c>
+      <c r="I5" t="s">
+        <v>68</v>
+      </c>
+      <c r="J5" t="s">
+        <v>35</v>
+      </c>
+      <c r="K5" t="s">
+        <v>36</v>
+      </c>
+      <c r="L5" t="s">
+        <v>37</v>
+      </c>
+      <c r="M5" t="s">
+        <v>69</v>
+      </c>
+      <c r="N5" t="s">
+        <v>70</v>
+      </c>
+      <c r="P5" t="s">
+        <v>71</v>
+      </c>
+      <c r="R5" t="s">
+        <v>72</v>
+      </c>
+      <c r="S5" t="s">
+        <v>43</v>
+      </c>
+      <c r="T5" t="s">
+        <v>73</v>
+      </c>
+      <c r="U5" t="s">
+        <v>74</v>
+      </c>
+      <c r="V5" t="s">
+        <v>75</v>
+      </c>
+      <c r="W5" t="s">
+        <v>76</v>
+      </c>
+      <c r="X5" t="s">
+        <v>77</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="6" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>79</v>
+      </c>
+      <c r="B6" t="s">
+        <v>80</v>
+      </c>
+      <c r="C6" t="s">
+        <v>81</v>
+      </c>
+      <c r="D6">
+        <v>16</v>
+      </c>
+      <c r="E6" t="s">
+        <v>82</v>
+      </c>
+      <c r="F6" t="s">
+        <v>31</v>
+      </c>
+      <c r="G6" t="s">
+        <v>83</v>
+      </c>
+      <c r="H6" t="s">
+        <v>84</v>
+      </c>
+      <c r="I6" t="s">
+        <v>85</v>
+      </c>
+      <c r="J6" t="s">
+        <v>86</v>
+      </c>
+      <c r="K6" t="s">
+        <v>87</v>
+      </c>
+      <c r="L6" t="s">
+        <v>88</v>
+      </c>
+      <c r="M6" t="s">
+        <v>89</v>
+      </c>
+      <c r="N6" t="s">
+        <v>90</v>
+      </c>
+      <c r="P6" t="s">
+        <v>91</v>
+      </c>
+      <c r="R6" t="s">
+        <v>92</v>
+      </c>
+      <c r="S6" t="s">
+        <v>93</v>
+      </c>
+      <c r="T6" t="s">
+        <v>94</v>
+      </c>
+      <c r="U6" t="s">
+        <v>74</v>
+      </c>
+      <c r="V6" t="s">
+        <v>95</v>
+      </c>
+      <c r="W6" t="s">
+        <v>96</v>
+      </c>
+      <c r="X6" t="s">
+        <v>97</v>
+      </c>
+      <c r="Y6" t="s">
+        <v>98</v>
+      </c>
+      <c r="Z6" t="s">
+        <v>99</v>
+      </c>
+      <c r="AA6" t="s">
+        <v>100</v>
+      </c>
+      <c r="AB6" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="7" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>102</v>
+      </c>
+      <c r="B7" t="s">
+        <v>29</v>
+      </c>
+      <c r="C7" t="s">
+        <v>79</v>
+      </c>
+      <c r="D7">
+        <v>8</v>
+      </c>
+      <c r="E7" t="s">
+        <v>103</v>
+      </c>
+      <c r="F7" t="s">
+        <v>31</v>
+      </c>
+      <c r="G7" t="s">
+        <v>104</v>
+      </c>
+      <c r="H7" t="s">
+        <v>33</v>
+      </c>
+      <c r="I7" t="s">
+        <v>105</v>
+      </c>
+      <c r="J7" t="s">
+        <v>35</v>
+      </c>
+      <c r="K7" t="s">
+        <v>36</v>
+      </c>
+      <c r="L7" t="s">
+        <v>37</v>
+      </c>
+      <c r="M7" t="s">
+        <v>89</v>
+      </c>
+      <c r="N7" t="s">
+        <v>106</v>
+      </c>
+      <c r="P7" t="s">
+        <v>91</v>
+      </c>
+      <c r="R7" t="s">
+        <v>107</v>
+      </c>
+      <c r="S7" t="s">
+        <v>43</v>
+      </c>
+      <c r="T7" t="s">
+        <v>94</v>
+      </c>
+      <c r="U7" t="s">
+        <v>108</v>
+      </c>
+      <c r="V7" t="s">
+        <v>95</v>
+      </c>
+      <c r="W7" t="s">
+        <v>96</v>
+      </c>
+      <c r="X7" t="s">
+        <v>97</v>
+      </c>
+      <c r="Y7" t="s">
+        <v>98</v>
+      </c>
+      <c r="Z7" t="s">
+        <v>99</v>
+      </c>
+      <c r="AA7" t="s">
+        <v>100</v>
+      </c>
+      <c r="AB7" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="8" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>109</v>
+      </c>
+      <c r="B8" t="s">
+        <v>29</v>
+      </c>
+      <c r="D8">
+        <v>0</v>
+      </c>
+      <c r="E8" t="s">
+        <v>110</v>
+      </c>
+      <c r="F8" t="s">
+        <v>52</v>
+      </c>
+      <c r="G8" t="s">
+        <v>111</v>
+      </c>
+      <c r="H8" t="s">
+        <v>33</v>
+      </c>
+      <c r="I8" t="s">
+        <v>112</v>
+      </c>
+      <c r="J8" t="s">
+        <v>35</v>
+      </c>
+      <c r="K8" t="s">
+        <v>36</v>
+      </c>
+      <c r="L8" t="s">
+        <v>37</v>
+      </c>
+      <c r="M8" t="s">
+        <v>113</v>
+      </c>
+      <c r="N8" t="s">
+        <v>114</v>
+      </c>
+      <c r="P8" t="s">
+        <v>115</v>
+      </c>
+      <c r="R8" t="s">
+        <v>116</v>
+      </c>
+      <c r="S8" t="s">
+        <v>43</v>
+      </c>
+      <c r="T8" t="s">
+        <v>117</v>
+      </c>
+      <c r="U8" t="s">
+        <v>118</v>
+      </c>
+      <c r="V8" t="s">
+        <v>119</v>
+      </c>
+      <c r="W8" t="s">
+        <v>120</v>
+      </c>
+      <c r="X8" t="s">
+        <v>121</v>
+      </c>
+      <c r="Y8" t="s">
+        <v>122</v>
+      </c>
+      <c r="Z8" t="s">
+        <v>123</v>
+      </c>
+      <c r="AA8" t="s">
+        <v>124</v>
+      </c>
+      <c r="AB8" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="9" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>126</v>
+      </c>
+      <c r="B9" t="s">
+        <v>29</v>
+      </c>
+      <c r="D9">
+        <v>0</v>
+      </c>
+      <c r="E9" t="s">
+        <v>127</v>
+      </c>
+      <c r="F9" t="s">
+        <v>31</v>
+      </c>
+      <c r="G9" t="s">
+        <v>128</v>
+      </c>
+      <c r="H9" t="s">
+        <v>33</v>
+      </c>
+      <c r="I9" t="s">
+        <v>129</v>
+      </c>
+      <c r="J9" t="s">
+        <v>35</v>
+      </c>
+      <c r="K9" t="s">
+        <v>36</v>
+      </c>
+      <c r="L9" t="s">
+        <v>37</v>
+      </c>
+      <c r="M9" t="s">
+        <v>113</v>
+      </c>
+      <c r="N9" t="s">
+        <v>130</v>
+      </c>
+      <c r="P9" t="s">
+        <v>131</v>
+      </c>
+      <c r="R9" t="s">
+        <v>132</v>
+      </c>
+      <c r="S9" t="s">
+        <v>43</v>
+      </c>
+      <c r="T9" t="s">
+        <v>133</v>
+      </c>
+      <c r="U9" t="s">
+        <v>134</v>
+      </c>
+      <c r="V9" t="s">
+        <v>135</v>
+      </c>
+      <c r="W9" t="s">
+        <v>136</v>
+      </c>
+      <c r="X9" t="s">
+        <v>137</v>
+      </c>
+      <c r="Y9" t="s">
+        <v>122</v>
+      </c>
+      <c r="Z9" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="10" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>139</v>
+      </c>
+      <c r="B10" t="s">
+        <v>140</v>
+      </c>
+      <c r="C10" t="s">
+        <v>141</v>
+      </c>
+      <c r="D10">
+        <v>47</v>
+      </c>
+      <c r="E10" t="s">
+        <v>142</v>
+      </c>
+      <c r="F10" t="s">
+        <v>31</v>
+      </c>
+      <c r="G10" t="s">
+        <v>143</v>
+      </c>
+      <c r="H10" t="s">
+        <v>33</v>
+      </c>
+      <c r="I10" t="s">
+        <v>144</v>
+      </c>
+      <c r="J10" t="s">
+        <v>145</v>
+      </c>
+      <c r="K10" t="s">
+        <v>146</v>
+      </c>
+      <c r="L10" t="s">
+        <v>147</v>
+      </c>
+      <c r="M10" t="s">
+        <v>113</v>
+      </c>
+      <c r="N10" t="s">
+        <v>90</v>
+      </c>
+      <c r="P10" t="s">
+        <v>131</v>
+      </c>
+      <c r="R10" t="s">
+        <v>148</v>
+      </c>
+      <c r="S10" t="s">
+        <v>93</v>
+      </c>
+      <c r="T10" t="s">
+        <v>149</v>
+      </c>
+      <c r="U10" t="s">
+        <v>150</v>
+      </c>
+      <c r="V10" t="s">
+        <v>151</v>
+      </c>
+      <c r="W10" t="s">
+        <v>152</v>
+      </c>
+      <c r="X10" t="s">
+        <v>153</v>
+      </c>
+      <c r="Y10" t="s">
+        <v>122</v>
+      </c>
+      <c r="Z10" t="s">
+        <v>154</v>
+      </c>
+      <c r="AA10" t="s">
+        <v>155</v>
+      </c>
+      <c r="AB10" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="11" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>157</v>
+      </c>
+      <c r="B11" t="s">
+        <v>29</v>
+      </c>
+      <c r="C11" t="s">
+        <v>139</v>
+      </c>
+      <c r="D11">
+        <v>10</v>
+      </c>
+      <c r="E11" t="s">
+        <v>158</v>
+      </c>
+      <c r="F11" t="s">
+        <v>31</v>
+      </c>
+      <c r="G11" t="s">
+        <v>159</v>
+      </c>
+      <c r="H11" t="s">
+        <v>33</v>
+      </c>
+      <c r="I11" t="s">
+        <v>160</v>
+      </c>
+      <c r="J11" t="s">
+        <v>35</v>
+      </c>
+      <c r="K11" t="s">
+        <v>161</v>
+      </c>
+      <c r="L11" t="s">
+        <v>37</v>
+      </c>
+      <c r="M11" t="s">
+        <v>113</v>
+      </c>
+      <c r="N11" t="s">
+        <v>162</v>
+      </c>
+      <c r="P11" t="s">
+        <v>131</v>
+      </c>
+      <c r="R11" t="s">
+        <v>163</v>
+      </c>
+      <c r="S11" t="s">
+        <v>93</v>
+      </c>
+      <c r="T11" t="s">
+        <v>149</v>
+      </c>
+      <c r="U11" t="s">
+        <v>164</v>
+      </c>
+      <c r="V11" t="s">
+        <v>151</v>
+      </c>
+      <c r="W11" t="s">
+        <v>152</v>
+      </c>
+      <c r="X11" t="s">
+        <v>153</v>
+      </c>
+      <c r="Y11" t="s">
+        <v>122</v>
+      </c>
+      <c r="Z11" t="s">
+        <v>154</v>
+      </c>
+      <c r="AA11" t="s">
+        <v>155</v>
+      </c>
+      <c r="AB11" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="12" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>165</v>
+      </c>
+      <c r="B12" t="s">
+        <v>29</v>
+      </c>
+      <c r="D12">
+        <v>0</v>
+      </c>
+      <c r="E12" t="s">
+        <v>166</v>
+      </c>
+      <c r="F12" t="s">
+        <v>31</v>
+      </c>
+      <c r="G12" t="s">
+        <v>167</v>
+      </c>
+      <c r="H12" t="s">
+        <v>33</v>
+      </c>
+      <c r="I12" t="s">
+        <v>168</v>
+      </c>
+      <c r="J12" t="s">
+        <v>35</v>
+      </c>
+      <c r="K12" t="s">
+        <v>36</v>
+      </c>
+      <c r="L12" t="s">
+        <v>37</v>
+      </c>
+      <c r="M12" t="s">
+        <v>113</v>
+      </c>
+      <c r="N12" t="s">
+        <v>169</v>
+      </c>
+      <c r="P12" t="s">
+        <v>131</v>
+      </c>
+      <c r="R12" t="s">
+        <v>170</v>
+      </c>
+      <c r="S12" t="s">
+        <v>43</v>
+      </c>
+      <c r="T12" t="s">
+        <v>171</v>
+      </c>
+      <c r="U12" t="s">
+        <v>172</v>
+      </c>
+      <c r="V12" t="s">
+        <v>173</v>
+      </c>
+      <c r="W12" t="s">
+        <v>174</v>
+      </c>
+      <c r="Y12" t="s">
+        <v>122</v>
+      </c>
+      <c r="Z12" t="s">
+        <v>175</v>
+      </c>
+      <c r="AA12" t="s">
+        <v>176</v>
+      </c>
+      <c r="AB12" t="s">
+        <v>177</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B11"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>GEO_ID</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>GSE200185119</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Error in `httr2::req_perform()`:
-! HTTP 404 Not Found.
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>GSE200214007</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Error in `httr2::req_perform()`:
-! HTTP 404 Not Found.
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>GSE200272695</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Error in `httr2::req_perform()`:
-! HTTP 404 Not Found.
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>GSE200247712</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Error in `httr2::req_perform()`:
-! HTTP 404 Not Found.
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>GSE200247711</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Error in `httr2::req_perform()`:
-! HTTP 404 Not Found.
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>GSE200230783</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Error in `httr2::req_perform()`:
-! HTTP 404 Not Found.
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>GSE200232526</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Error in `httr2::req_perform()`:
-! HTTP 404 Not Found.
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>GSE200270174</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Error in `httr2::req_perform()`:
-! HTTP 404 Not Found.
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>GSE200270170</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Error in `httr2::req_perform()`:
-! HTTP 404 Not Found.
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>GSE200232692</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Error in `httr2::req_perform()`:
-! HTTP 404 Not Found.
-</t>
-        </is>
+    <row r="1" spans="1:1" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>178</v>
       </c>
     </row>
   </sheetData>
